--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>108203</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585926.3713565771</v>
+        <v>585926</v>
       </c>
       <c r="R2" t="n">
-        <v>6421152.528347835</v>
+        <v>6421153</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1979-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1983-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110713</v>
+        <v>110722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110722</v>
+        <v>110727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110727</v>
+        <v>110755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110755</v>
+        <v>110761</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110761</v>
+        <v>110768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110768</v>
+        <v>110772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110772</v>
+        <v>110780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110783</v>
+        <v>110788</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110788</v>
+        <v>110796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23186-2025 artfynd.xlsx
+++ b/artfynd/A 23186-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74977078</v>
       </c>
       <c r="B2" t="n">
-        <v>110796</v>
+        <v>110806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
